--- a/kevin1.xlsx
+++ b/kevin1.xlsx
@@ -4,18 +4,21 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10848" windowHeight="8952" activeTab="1"/>
+    <workbookView windowWidth="10848" windowHeight="9000" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="origin" sheetId="1" r:id="rId1"/>
     <sheet name="exercise" sheetId="2" r:id="rId2"/>
+    <sheet name="origin2" sheetId="3" r:id="rId3"/>
+    <sheet name="exercise2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -70,16 +73,55 @@
   <si>
     <t>Q4</t>
   </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Excel Charts and Graphs Tutorial</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>7/1/2026</t>
+  </si>
+  <si>
+    <t>8/1/2026</t>
+  </si>
+  <si>
+    <t>9/1/2026</t>
+  </si>
+  <si>
+    <t>10/1/2026</t>
+  </si>
+  <si>
+    <t>11/1/2026</t>
+  </si>
+  <si>
+    <t>12/1/2026</t>
+  </si>
+  <si>
+    <t>choco</t>
+  </si>
+  <si>
+    <t>raisin</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>fortune</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -105,7 +147,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -113,6 +170,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -127,9 +191,48 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -138,21 +241,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -166,55 +254,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,16 +268,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,19 +298,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -292,13 +388,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,43 +442,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -358,85 +478,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,6 +511,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -483,26 +540,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,8 +567,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -573,145 +615,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -829,6 +871,7 @@
               <a:rPr lang="en-US" altLang="ja-JP"/>
               <a:t>Sales</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" altLang="ja-JP"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1118,7 +1161,1551 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="ja-JP" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" altLang="ja-JP">
+                <a:latin typeface="Calibri" panose="020F0502020204030204" charset="0"/>
+              </a:rPr>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" altLang="ja-JP">
+              <a:latin typeface="Calibri" panose="020F0502020204030204" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>origin2!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Month</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>origin2!$A$4:$A$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>origin2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:forward val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>origin2!$B$4:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45212</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22816</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38542</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48546</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24521</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25479</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32312</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46358</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48774</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>55485</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>78542</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="493026505"/>
+        <c:axId val="654120748"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="493026505"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="654120748"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="654120748"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="493026505"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="ja-JP"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="ja-JP" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>choco</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" c:formatCode="General">
+                  <c:v>7/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="General">
+                  <c:v>8/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="General">
+                  <c:v>9/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="General">
+                  <c:v>10/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="General">
+                  <c:v>11/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="General">
+                  <c:v>12/1/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$2:$G$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>25479</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32312</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46358</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48774</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55485</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78542</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>raisin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" c:formatCode="General">
+                  <c:v>7/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="General">
+                  <c:v>8/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="General">
+                  <c:v>9/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="General">
+                  <c:v>10/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="General">
+                  <c:v>11/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="General">
+                  <c:v>12/1/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>21091</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9455</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48425</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16687</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18540</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31056</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>sugar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" c:formatCode="General">
+                  <c:v>7/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="General">
+                  <c:v>8/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="General">
+                  <c:v>9/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="General">
+                  <c:v>10/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="General">
+                  <c:v>11/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="General">
+                  <c:v>12/1/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>24731</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8329</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25352</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38141</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36935</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15947</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>fortune</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$1:$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" c:formatCode="General">
+                  <c:v>7/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="General">
+                  <c:v>8/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="General">
+                  <c:v>9/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="General">
+                  <c:v>10/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="General">
+                  <c:v>11/1/2026</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="General">
+                  <c:v>12/1/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7165</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16771</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26401</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23721</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17863</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="464623115"/>
+        <c:axId val="625874733"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="464623115"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="625874733"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="625874733"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="464623115"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="ja-JP"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10625"/>
+          <c:y val="0.191666666666667"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="ja-JP" sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr/>
+          <c:explosion val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent1"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent1"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent2"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent2"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent3"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent3"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="ltUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="accent4"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent4"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$10:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0" c:formatCode="General">
+                  <c:v>choco</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="General">
+                  <c:v>raisin</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="General">
+                  <c:v>sugar</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="General">
+                  <c:v>fortune</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$10:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>286950</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>145254</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>149435</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>113521</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="ja-JP"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1661,6 +3248,1559 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="252">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1688,6 +4828,106 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="1460500" y="1043940"/>
+        <a:ext cx="4572000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>500380</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>195580</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="1719580" y="1051560"/>
+        <a:ext cx="4572000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>149860</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>454660</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="グラフ 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="149860" y="2956560"/>
+        <a:ext cx="4572000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2213,4 +5453,513 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>45212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>22816</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>38542</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>48546</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>24521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>25479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>32312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>48774</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>55485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>78542</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <f>SUM(B4:B15)</f>
+        <v>470712</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A31" r:id="rId2" display="Excel Charts and Graphs Tutorial" tooltip="https://www.youtube.com/watch?v=eHtZrIb0oWY"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A4:B16"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>45212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>22816</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>38542</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>48546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>24521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>25479</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>32312</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>48774</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>55485</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>78542</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>25479</v>
+      </c>
+      <c r="C2">
+        <v>32312</v>
+      </c>
+      <c r="D2">
+        <v>46358</v>
+      </c>
+      <c r="E2">
+        <v>48774</v>
+      </c>
+      <c r="F2">
+        <v>55485</v>
+      </c>
+      <c r="G2">
+        <v>78542</v>
+      </c>
+      <c r="I2">
+        <f>SUM(B2:G2)</f>
+        <v>286950</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>21091</v>
+      </c>
+      <c r="C3">
+        <v>9455</v>
+      </c>
+      <c r="D3">
+        <v>48425</v>
+      </c>
+      <c r="E3">
+        <v>16687</v>
+      </c>
+      <c r="F3">
+        <v>18540</v>
+      </c>
+      <c r="G3">
+        <v>31056</v>
+      </c>
+      <c r="I3">
+        <f>SUM(B3:G3)</f>
+        <v>145254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>24731</v>
+      </c>
+      <c r="C4">
+        <v>8329</v>
+      </c>
+      <c r="D4">
+        <v>25352</v>
+      </c>
+      <c r="E4">
+        <v>38141</v>
+      </c>
+      <c r="F4">
+        <v>36935</v>
+      </c>
+      <c r="G4">
+        <v>15947</v>
+      </c>
+      <c r="I4">
+        <f>SUM(B4:G4)</f>
+        <v>149435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>7165</v>
+      </c>
+      <c r="C5">
+        <v>21600</v>
+      </c>
+      <c r="D5">
+        <v>16771</v>
+      </c>
+      <c r="E5">
+        <v>26401</v>
+      </c>
+      <c r="F5">
+        <v>23721</v>
+      </c>
+      <c r="G5">
+        <v>17863</v>
+      </c>
+      <c r="I5">
+        <f>SUM(B5:G5)</f>
+        <v>113521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>286950</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>145254</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12">
+        <v>149435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <v>113521</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup type="line" displayEmptyCellsAs="gap">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet3!B2:G2</xm:f>
+              <xm:sqref>H2</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="line" displayEmptyCellsAs="gap">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet3!B3:G3</xm:f>
+              <xm:sqref>H3</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="line" displayEmptyCellsAs="gap">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet3!B4:G4</xm:f>
+              <xm:sqref>H4</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="line" displayEmptyCellsAs="gap">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet3!B5:G5</xm:f>
+              <xm:sqref>H5</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/kevin1.xlsx
+++ b/kevin1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10848" windowHeight="9000" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="10848" windowHeight="9000" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="origin" sheetId="1" r:id="rId1"/>
@@ -12,13 +12,18 @@
     <sheet name="origin2" sheetId="3" r:id="rId3"/>
     <sheet name="exercise2" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId8"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -118,9 +123,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -139,6 +144,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -146,8 +159,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -155,6 +176,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,20 +196,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -190,8 +204,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,14 +251,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -246,31 +268,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,7 +303,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,25 +417,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,151 +487,124 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="20">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFABABAB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFABABAB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFABABAB"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFABABAB"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -525,6 +641,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -540,15 +667,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -560,6 +678,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,17 +723,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -615,153 +731,180 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -770,7 +913,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4936,6 +5079,142 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46182.2984722222" refreshedBy="user" recordCount="4">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="H1:N5" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Type" numFmtId="0">
+      <sharedItems count="4">
+        <s v="choco"/>
+        <s v="raisin"/>
+        <s v="sugar"/>
+        <s v="fortune"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="7/1/2026" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7165" maxValue="25479" count="4">
+        <n v="25479"/>
+        <n v="21091"/>
+        <n v="24731"/>
+        <n v="7165"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="8/1/2026" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8329" maxValue="32312" count="4">
+        <n v="32312"/>
+        <n v="9455"/>
+        <n v="8329"/>
+        <n v="21600"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="9/1/2026" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="16771" maxValue="48425" count="4">
+        <n v="46358"/>
+        <n v="48425"/>
+        <n v="25352"/>
+        <n v="16771"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="10/1/2026" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="16687" maxValue="48774" count="4">
+        <n v="48774"/>
+        <n v="16687"/>
+        <n v="38141"/>
+        <n v="26401"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="11/1/2026" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="18540" maxValue="55485" count="4">
+        <n v="55485"/>
+        <n v="18540"/>
+        <n v="36935"/>
+        <n v="23721"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="12/1/2026" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15947" maxValue="78542" count="4">
+        <n v="78542"/>
+        <n v="31056"/>
+        <n v="15947"/>
+        <n v="17863"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="4">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ピボットテーブル1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
+  <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="7">
+    <pivotField compact="0" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -5327,106 +5606,106 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="11">
         <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="12">
         <v>1800</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="11">
         <v>2400</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="12">
         <v>3200</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="11">
         <v>4100</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="12">
         <v>5000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="11">
         <v>6200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="12">
         <v>6800</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="11">
         <v>5900</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="12">
         <v>7200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="11">
         <v>9500</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="13">
         <v>14500</v>
       </c>
     </row>
@@ -5962,4 +6241,504 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:C20"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="5.88888888888889"/>
+    <col min="2" max="2" width="10.4444444444444"/>
+    <col min="3" max="5" width="7.88888888888889"/>
+    <col min="6" max="6" width="6.66666666666667"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2">
+        <v>25479</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2">
+        <v>25479</v>
+      </c>
+      <c r="J2">
+        <v>32312</v>
+      </c>
+      <c r="K2">
+        <v>46358</v>
+      </c>
+      <c r="L2">
+        <v>48774</v>
+      </c>
+      <c r="M2">
+        <v>55485</v>
+      </c>
+      <c r="N2">
+        <v>78542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
+        <v>21091</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3">
+        <v>21091</v>
+      </c>
+      <c r="J3">
+        <v>9455</v>
+      </c>
+      <c r="K3">
+        <v>48425</v>
+      </c>
+      <c r="L3">
+        <v>16687</v>
+      </c>
+      <c r="M3">
+        <v>18540</v>
+      </c>
+      <c r="N3">
+        <v>31056</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>24731</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4">
+        <v>24731</v>
+      </c>
+      <c r="J4">
+        <v>8329</v>
+      </c>
+      <c r="K4">
+        <v>25352</v>
+      </c>
+      <c r="L4">
+        <v>38141</v>
+      </c>
+      <c r="M4">
+        <v>36935</v>
+      </c>
+      <c r="N4">
+        <v>15947</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>7165</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>7165</v>
+      </c>
+      <c r="J5">
+        <v>21600</v>
+      </c>
+      <c r="K5">
+        <v>16771</v>
+      </c>
+      <c r="L5">
+        <v>26401</v>
+      </c>
+      <c r="M5">
+        <v>23721</v>
+      </c>
+      <c r="N5">
+        <v>17863</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>32312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>9455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>8329</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>48425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>25352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>16771</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>48774</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15">
+        <v>16687</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>38141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>26401</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>55485</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>18540</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>36935</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>23721</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>78542</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23">
+        <v>31056</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>15947</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25">
+        <v>17863</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/kevin1.xlsx
+++ b/kevin1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10848" windowHeight="9000" firstSheet="4" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="9144" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="origin" sheetId="1" r:id="rId1"/>
@@ -13,17 +13,19 @@
     <sheet name="exercise2" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId7"/>
+    <sheet name="pivot" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="144525"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="33">
   <si>
     <t>Date</t>
   </si>
@@ -117,6 +119,12 @@
   <si>
     <t>fortune</t>
   </si>
+  <si>
+    <t>合計:Sales</t>
+  </si>
+  <si>
+    <t>総計</t>
+  </si>
 </sst>
 </file>
 
@@ -125,8 +133,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -146,22 +154,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -175,14 +176,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,9 +197,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,22 +213,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,6 +231,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -268,14 +275,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,24 +311,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -333,19 +323,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,73 +341,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +359,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,25 +413,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,7 +449,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,6 +635,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -637,17 +660,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -667,17 +679,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -731,58 +739,58 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -791,85 +799,85 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2728,6 +2736,445 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[kevin1.xlsx]pivot!ピボットテーブル1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>pivot!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>集計</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>pivot!$A$4:$B$34</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="24"/>
+                <c:lvl>
+                  <c:pt idx="0" c:formatCode="General">
+                    <c:v>choco</c:v>
+                  </c:pt>
+                  <c:pt idx="1" c:formatCode="General">
+                    <c:v>fortune</c:v>
+                  </c:pt>
+                  <c:pt idx="2" c:formatCode="General">
+                    <c:v>raisin</c:v>
+                  </c:pt>
+                  <c:pt idx="3" c:formatCode="General">
+                    <c:v>sugar</c:v>
+                  </c:pt>
+                  <c:pt idx="4" c:formatCode="General">
+                    <c:v>choco</c:v>
+                  </c:pt>
+                  <c:pt idx="5" c:formatCode="General">
+                    <c:v>fortune</c:v>
+                  </c:pt>
+                  <c:pt idx="6" c:formatCode="General">
+                    <c:v>raisin</c:v>
+                  </c:pt>
+                  <c:pt idx="7" c:formatCode="General">
+                    <c:v>sugar</c:v>
+                  </c:pt>
+                  <c:pt idx="8" c:formatCode="General">
+                    <c:v>choco</c:v>
+                  </c:pt>
+                  <c:pt idx="9" c:formatCode="General">
+                    <c:v>fortune</c:v>
+                  </c:pt>
+                  <c:pt idx="10" c:formatCode="General">
+                    <c:v>raisin</c:v>
+                  </c:pt>
+                  <c:pt idx="11" c:formatCode="General">
+                    <c:v>sugar</c:v>
+                  </c:pt>
+                  <c:pt idx="12" c:formatCode="General">
+                    <c:v>choco</c:v>
+                  </c:pt>
+                  <c:pt idx="13" c:formatCode="General">
+                    <c:v>fortune</c:v>
+                  </c:pt>
+                  <c:pt idx="14" c:formatCode="General">
+                    <c:v>raisin</c:v>
+                  </c:pt>
+                  <c:pt idx="15" c:formatCode="General">
+                    <c:v>sugar</c:v>
+                  </c:pt>
+                  <c:pt idx="16" c:formatCode="General">
+                    <c:v>choco</c:v>
+                  </c:pt>
+                  <c:pt idx="17" c:formatCode="General">
+                    <c:v>fortune</c:v>
+                  </c:pt>
+                  <c:pt idx="18" c:formatCode="General">
+                    <c:v>raisin</c:v>
+                  </c:pt>
+                  <c:pt idx="19" c:formatCode="General">
+                    <c:v>sugar</c:v>
+                  </c:pt>
+                  <c:pt idx="20" c:formatCode="General">
+                    <c:v>choco</c:v>
+                  </c:pt>
+                  <c:pt idx="21" c:formatCode="General">
+                    <c:v>fortune</c:v>
+                  </c:pt>
+                  <c:pt idx="22" c:formatCode="General">
+                    <c:v>raisin</c:v>
+                  </c:pt>
+                  <c:pt idx="23" c:formatCode="General">
+                    <c:v>sugar</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0" c:formatCode="General">
+                    <c:v>10/1/2026</c:v>
+                  </c:pt>
+                  <c:pt idx="4" c:formatCode="General">
+                    <c:v>11/1/2026</c:v>
+                  </c:pt>
+                  <c:pt idx="8" c:formatCode="General">
+                    <c:v>12/1/2026</c:v>
+                  </c:pt>
+                  <c:pt idx="12" c:formatCode="General">
+                    <c:v>7/1/2026</c:v>
+                  </c:pt>
+                  <c:pt idx="16" c:formatCode="General">
+                    <c:v>8/1/2026</c:v>
+                  </c:pt>
+                  <c:pt idx="20" c:formatCode="General">
+                    <c:v>9/1/2026</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>pivot!$C$4:$C$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>48774</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26401</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16687</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38141</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55485</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23721</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18540</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36935</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>78542</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17863</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31056</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>15947</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>25479</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7165</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21091</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24731</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>32312</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>21600</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9455</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8329</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46358</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>16771</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>48425</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>25352</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="953425559"/>
+        <c:axId val="277466882"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="953425559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="277466882"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="277466882"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953425559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="ja-JP" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="ja-JP"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2888,6 +3335,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -4940,6 +5427,509 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -5079,6 +6069,41 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2778760" y="480060"/>
+        <a:ext cx="4572000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46182.2984722222" refreshedBy="user" recordCount="4">
   <cacheSource type="worksheet">
@@ -5094,7 +6119,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="7/1/2026" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7165" maxValue="25479" count="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="25479" count="4">
         <n v="25479"/>
         <n v="21091"/>
         <n v="24731"/>
@@ -5102,7 +6127,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="8/1/2026" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8329" maxValue="32312" count="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="32312" count="4">
         <n v="32312"/>
         <n v="9455"/>
         <n v="8329"/>
@@ -5110,7 +6135,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="9/1/2026" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="16771" maxValue="48425" count="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="48425" count="4">
         <n v="46358"/>
         <n v="48425"/>
         <n v="25352"/>
@@ -5118,7 +6143,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="10/1/2026" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="16687" maxValue="48774" count="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="48774" count="4">
         <n v="48774"/>
         <n v="16687"/>
         <n v="38141"/>
@@ -5126,7 +6151,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="11/1/2026" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="18540" maxValue="55485" count="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="55485" count="4">
         <n v="55485"/>
         <n v="18540"/>
         <n v="36935"/>
@@ -5134,7 +6159,63 @@
       </sharedItems>
     </cacheField>
     <cacheField name="12/1/2026" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15947" maxValue="78542" count="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="78542" count="4">
+        <n v="78542"/>
+        <n v="31056"/>
+        <n v="15947"/>
+        <n v="17863"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46184.8056712963" refreshedBy="user" recordCount="24">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:C25" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Type" numFmtId="0">
+      <sharedItems count="4">
+        <s v="choco"/>
+        <s v="raisin"/>
+        <s v="sugar"/>
+        <s v="fortune"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Month" numFmtId="0">
+      <sharedItems count="6">
+        <s v="7/1/2026"/>
+        <s v="8/1/2026"/>
+        <s v="9/1/2026"/>
+        <s v="10/1/2026"/>
+        <s v="11/1/2026"/>
+        <s v="12/1/2026"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7165" maxValue="78542" count="24">
+        <n v="25479"/>
+        <n v="21091"/>
+        <n v="24731"/>
+        <n v="7165"/>
+        <n v="32312"/>
+        <n v="9455"/>
+        <n v="8329"/>
+        <n v="21600"/>
+        <n v="46358"/>
+        <n v="48425"/>
+        <n v="25352"/>
+        <n v="16771"/>
+        <n v="48774"/>
+        <n v="16687"/>
+        <n v="38141"/>
+        <n v="26401"/>
+        <n v="55485"/>
+        <n v="18540"/>
+        <n v="36935"/>
+        <n v="23721"/>
         <n v="78542"/>
         <n v="31056"/>
         <n v="15947"/>
@@ -5186,6 +6267,131 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="24">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="19"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="20"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="21"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="22"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="23"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ピボットテーブル1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
@@ -5206,6 +6412,146 @@
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
   </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ピボットテーブル1" cacheId="1" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="値" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:C34" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="31">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="合計:Sales" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -6354,6 +7700,287 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A3:C34"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778"/>
+    <col min="2" max="2" width="8.33333333333333"/>
+    <col min="3" max="3" width="11.7777777777778"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4">
+        <v>130003</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>48774</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>26401</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>16687</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>38141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9">
+        <v>134681</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>55485</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>23721</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <v>18540</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>36935</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14"/>
+      <c r="C14">
+        <v>143408</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15">
+        <v>78542</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>17863</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17">
+        <v>31056</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>15947</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19"/>
+      <c r="C19">
+        <v>78466</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>25479</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>7165</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>21091</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>24731</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24">
+        <v>71696</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <v>32312</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <v>9455</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28">
+        <v>8329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>136906</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>16771</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>48425</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33">
+        <v>25352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>695160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2"/>
   <sheetData>
